--- a/InputData/elec/GHESS/Green Hydrogen Electricity Supply Shareweights.xlsx
+++ b/InputData/elec/GHESS/Green Hydrogen Electricity Supply Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28627"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\GHESS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\eps-mexico\InputData\elec\GHESS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E51E6-BA89-4879-AFE0-0753A63A9214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA78B254-6030-4733-8820-606A1BF9082B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -148,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1216,55 +1216,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="61.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -1280,13 +1280,13 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:AY25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="45">
+    <row r="1" spans="1:51" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1380,68 @@
       <c r="AE1">
         <v>2050</v>
       </c>
+      <c r="AF1">
+        <v>2051</v>
+      </c>
+      <c r="AG1">
+        <v>2052</v>
+      </c>
+      <c r="AH1">
+        <v>2053</v>
+      </c>
+      <c r="AI1">
+        <v>2054</v>
+      </c>
+      <c r="AJ1">
+        <v>2055</v>
+      </c>
+      <c r="AK1">
+        <v>2056</v>
+      </c>
+      <c r="AL1">
+        <v>2057</v>
+      </c>
+      <c r="AM1">
+        <v>2058</v>
+      </c>
+      <c r="AN1">
+        <v>2059</v>
+      </c>
+      <c r="AO1">
+        <v>2060</v>
+      </c>
+      <c r="AP1">
+        <v>2061</v>
+      </c>
+      <c r="AQ1">
+        <v>2062</v>
+      </c>
+      <c r="AR1">
+        <v>2063</v>
+      </c>
+      <c r="AS1">
+        <v>2064</v>
+      </c>
+      <c r="AT1">
+        <v>2065</v>
+      </c>
+      <c r="AU1">
+        <v>2066</v>
+      </c>
+      <c r="AV1">
+        <v>2067</v>
+      </c>
+      <c r="AW1">
+        <v>2068</v>
+      </c>
+      <c r="AX1">
+        <v>2069</v>
+      </c>
+      <c r="AY1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1475,8 +1535,68 @@
       <c r="AE2">
         <v>0</v>
       </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1570,8 +1690,68 @@
       <c r="AE3">
         <v>0</v>
       </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1665,8 +1845,68 @@
       <c r="AE4">
         <v>0</v>
       </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1760,8 +2000,68 @@
       <c r="AE5">
         <v>0</v>
       </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1855,8 +2155,68 @@
       <c r="AE6">
         <v>0</v>
       </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1950,8 +2310,68 @@
       <c r="AE7">
         <v>1</v>
       </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <v>1</v>
+      </c>
+      <c r="AT7">
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <v>1</v>
+      </c>
+      <c r="AW7">
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2045,8 +2465,68 @@
       <c r="AE8">
         <v>1</v>
       </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2140,8 +2620,68 @@
       <c r="AE9">
         <v>0</v>
       </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <v>0</v>
+      </c>
+      <c r="AY9">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2235,8 +2775,68 @@
       <c r="AE10">
         <v>0</v>
       </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2330,8 +2930,68 @@
       <c r="AE11">
         <v>0</v>
       </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2425,8 +3085,68 @@
       <c r="AE12">
         <v>0</v>
       </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2520,8 +3240,68 @@
       <c r="AE13">
         <v>0</v>
       </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2615,8 +3395,68 @@
       <c r="AE14">
         <v>0</v>
       </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2710,8 +3550,68 @@
       <c r="AE15">
         <v>0</v>
       </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2805,8 +3705,68 @@
       <c r="AE16">
         <v>0</v>
       </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2900,8 +3860,68 @@
       <c r="AE17">
         <v>0</v>
       </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2995,8 +4015,68 @@
       <c r="AE18">
         <v>0</v>
       </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -3090,8 +4170,68 @@
       <c r="AE19">
         <v>0</v>
       </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <v>0</v>
+      </c>
+      <c r="AV19">
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <v>0</v>
+      </c>
+      <c r="AX19">
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:31">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3185,8 +4325,68 @@
       <c r="AE20">
         <v>0</v>
       </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -3280,8 +4480,68 @@
       <c r="AE21">
         <v>0</v>
       </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:31">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -3375,8 +4635,68 @@
       <c r="AE22">
         <v>0</v>
       </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -3470,8 +4790,68 @@
       <c r="AE23">
         <v>0</v>
       </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>32</v>
       </c>
@@ -3565,8 +4945,68 @@
       <c r="AE24">
         <v>0</v>
       </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
@@ -3658,6 +5098,66 @@
         <v>0</v>
       </c>
       <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
         <v>0</v>
       </c>
     </row>
@@ -3673,15 +5173,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -3825,14 +5316,46 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605A9E81-AB5D-4D2D-839D-73F353EB58DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{605A9E81-AB5D-4D2D-839D-73F353EB58DD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FCB382D-0D2F-44B1-A77F-18882D5DE184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C103DFDA-566E-4145-B13C-D728E6300F00}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C103DFDA-566E-4145-B13C-D728E6300F00}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FCB382D-0D2F-44B1-A77F-18882D5DE184}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>